--- a/output/daily_ratings/uk_ratings_2026-06-28.xlsx
+++ b/output/daily_ratings/uk_ratings_2026-06-28.xlsx
@@ -522,11 +522,11 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Alpine Wedding (IRE)</t>
+          <t>Alpha (IRE)</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -542,14 +542,16 @@
       <c r="M2" t="n">
         <v>83.91</v>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>81.8</v>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -576,11 +578,11 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Alpha (IRE)</t>
+          <t>Ibelieveicanfly (USA)</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -592,12 +594,14 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>6</v>
+      </c>
       <c r="M3" t="n">
         <v>83.91</v>
       </c>
       <c r="N3" t="n">
-        <v>81.8</v>
+        <v>62</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -632,11 +636,11 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Ibelieveicanfly (USA)</t>
+          <t>Livenka</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -649,13 +653,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>8.25</v>
       </c>
       <c r="M4" t="n">
         <v>83.91</v>
       </c>
       <c r="N4" t="n">
-        <v>62</v>
+        <v>57.4</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -690,11 +694,11 @@
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Livenka</t>
+          <t>Samnina (IRE)</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -707,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>8.25</v>
+        <v>8.75</v>
       </c>
       <c r="M5" t="n">
         <v>83.91</v>
       </c>
       <c r="N5" t="n">
-        <v>57.4</v>
+        <v>57</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -748,11 +752,11 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Samnina (IRE)</t>
+          <t>Pretty Thoughts (IRE)</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -765,13 +769,13 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
       <c r="M6" t="n">
         <v>83.91</v>
       </c>
       <c r="N6" t="n">
-        <v>57</v>
+        <v>50.1</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -806,11 +810,11 @@
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pretty Thoughts (IRE)</t>
+          <t>Isle Of Capri (IRE)</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -823,13 +827,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="M7" t="n">
         <v>83.91</v>
       </c>
       <c r="N7" t="n">
-        <v>50.1</v>
+        <v>49.5</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -864,11 +868,11 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Isle Of Capri (IRE)</t>
+          <t>Old Joanie (IRE)</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -881,13 +885,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>11</v>
+        <v>11.75</v>
       </c>
       <c r="M8" t="n">
         <v>83.91</v>
       </c>
       <c r="N8" t="n">
-        <v>49.5</v>
+        <v>46.2</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -922,11 +926,11 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Old Joanie (IRE)</t>
+          <t>Endless Night (IRE)</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -939,13 +943,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>11.75</v>
+        <v>13</v>
       </c>
       <c r="M9" t="n">
         <v>83.91</v>
       </c>
       <c r="N9" t="n">
-        <v>46.2</v>
+        <v>43.4</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -980,11 +984,11 @@
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Endless Night (IRE)</t>
+          <t>Alreem (IRE)</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -997,13 +1001,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="M10" t="n">
         <v>83.91</v>
       </c>
       <c r="N10" t="n">
-        <v>43.4</v>
+        <v>42.3</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1038,30 +1042,30 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Alreem (IRE)</t>
+          <t>Social Circle (IRE)</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>13.5</v>
+        <v>14.75</v>
       </c>
       <c r="M11" t="n">
         <v>83.91</v>
       </c>
       <c r="N11" t="n">
-        <v>42.3</v>
+        <v>34.4</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1096,11 +1100,11 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Social Circle (IRE)</t>
+          <t>Exchange Student (IRE)</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1113,13 +1117,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>14.75</v>
+        <v>16.5</v>
       </c>
       <c r="M12" t="n">
         <v>83.91</v>
       </c>
       <c r="N12" t="n">
-        <v>39</v>
+        <v>29.4</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1154,30 +1158,30 @@
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Exchange Student (IRE)</t>
+          <t>Exceptionally (USA)</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>16.5</v>
+        <v>16.65</v>
       </c>
       <c r="M13" t="n">
         <v>83.91</v>
       </c>
       <c r="N13" t="n">
-        <v>29.4</v>
+        <v>26</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1212,11 +1216,11 @@
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Exceptionally (USA)</t>
+          <t>Littlepacer (IRE)</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1229,13 +1233,13 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>16.65</v>
+        <v>19.9</v>
       </c>
       <c r="M14" t="n">
         <v>83.91</v>
       </c>
       <c r="N14" t="n">
-        <v>28.7</v>
+        <v>23.2</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1269,40 +1273,24 @@
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="n">
-        <v>13</v>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Littlepacer (IRE)</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>128</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M15" t="n">
-        <v>83.91</v>
-      </c>
-      <c r="N15" t="n">
-        <v>23.2</v>
-      </c>
+          <t>Alpine Wedding (IRE)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1328,34 +1316,36 @@
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Gazelle Dor (IRE)</t>
+          <t>Genesis (IRE)</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="K16" t="n">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
         <v>57.94</v>
       </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>73.90000000000001</v>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-17</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="17">
@@ -1382,28 +1372,30 @@
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Genesis (IRE)</t>
+          <t>Sarahmae (IRE)</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="K17" t="n">
-        <v>73</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.15</v>
+      </c>
       <c r="M17" t="n">
         <v>57.94</v>
       </c>
       <c r="N17" t="n">
-        <v>75.09999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1411,7 +1403,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1438,30 +1430,30 @@
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sarahmae (IRE)</t>
+          <t>Dark Ace (IRE)</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K18" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="L18" t="n">
-        <v>0.15</v>
+        <v>0.65</v>
       </c>
       <c r="M18" t="n">
         <v>57.94</v>
       </c>
       <c r="N18" t="n">
-        <v>87.2</v>
+        <v>82.3</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1496,30 +1488,30 @@
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Dark Ace (IRE)</t>
+          <t>Cuban Grey</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="K19" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="L19" t="n">
-        <v>0.65</v>
+        <v>1.15</v>
       </c>
       <c r="M19" t="n">
         <v>57.94</v>
       </c>
       <c r="N19" t="n">
-        <v>82.3</v>
+        <v>69.8</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1527,7 +1519,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="20">
@@ -1554,30 +1546,30 @@
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Cuban Grey</t>
+          <t>Back Down Under (IRE)</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K20" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L20" t="n">
-        <v>1.15</v>
+        <v>3.15</v>
       </c>
       <c r="M20" t="n">
         <v>57.94</v>
       </c>
       <c r="N20" t="n">
-        <v>69.8</v>
+        <v>63.7</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1585,7 +1577,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>-5</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="21">
@@ -1612,30 +1604,30 @@
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Back Down Under (IRE)</t>
+          <t>Toca Madera (IRE)</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>5</v>
       </c>
       <c r="J21" t="n">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="K21" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="L21" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="M21" t="n">
         <v>57.94</v>
       </c>
       <c r="N21" t="n">
-        <v>63.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1643,7 +1635,7 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>-6.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1670,30 +1662,30 @@
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Toca Madera (IRE)</t>
+          <t>Moltophino (IRE)</t>
         </is>
       </c>
       <c r="I22" t="n">
         <v>5</v>
       </c>
       <c r="J22" t="n">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="K22" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="L22" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="M22" t="n">
         <v>57.94</v>
       </c>
       <c r="N22" t="n">
-        <v>78.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1701,7 +1693,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="23">
@@ -1728,30 +1720,30 @@
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Moltophino (IRE)</t>
+          <t>Erosandpsyche (IRE)</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J23" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="K23" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="L23" t="n">
-        <v>3.21</v>
+        <v>3.96</v>
       </c>
       <c r="M23" t="n">
         <v>57.94</v>
       </c>
       <c r="N23" t="n">
-        <v>68.8</v>
+        <v>74.3</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1759,7 +1751,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1786,30 +1778,30 @@
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Erosandpsyche (IRE)</t>
+          <t>Likedbymike (IRE)</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K24" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L24" t="n">
-        <v>3.96</v>
+        <v>4.109999999999999</v>
       </c>
       <c r="M24" t="n">
         <v>57.94</v>
       </c>
       <c r="N24" t="n">
-        <v>74.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1817,7 +1809,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1844,30 +1836,30 @@
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Likedbymike (IRE)</t>
+          <t>Harrys Hill</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J25" t="n">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="K25" t="n">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="L25" t="n">
-        <v>4.11</v>
+        <v>4.26</v>
       </c>
       <c r="M25" t="n">
         <v>57.94</v>
       </c>
       <c r="N25" t="n">
-        <v>75.90000000000001</v>
+        <v>54.1</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1875,7 +1867,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="26">
@@ -1902,30 +1894,30 @@
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Harrys Hill</t>
+          <t>Kerdos (IRE)</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="K26" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="L26" t="n">
-        <v>4.26</v>
+        <v>4.41</v>
       </c>
       <c r="M26" t="n">
         <v>57.94</v>
       </c>
       <c r="N26" t="n">
-        <v>59.1</v>
+        <v>70.3</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -1933,7 +1925,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1960,30 +1952,30 @@
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kerdos (IRE)</t>
+          <t>Red Evolution (IRE)</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K27" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="L27" t="n">
-        <v>4.41</v>
+        <v>4.56</v>
       </c>
       <c r="M27" t="n">
         <v>57.94</v>
       </c>
       <c r="N27" t="n">
-        <v>73.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2018,30 +2010,30 @@
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Red Evolution (IRE)</t>
+          <t>Shadow Of The Moon (IRE)</t>
         </is>
       </c>
       <c r="I28" t="n">
         <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="K28" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="L28" t="n">
-        <v>4.56</v>
+        <v>5.06</v>
       </c>
       <c r="M28" t="n">
         <v>57.94</v>
       </c>
       <c r="N28" t="n">
-        <v>70.09999999999999</v>
+        <v>54.8</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2049,7 +2041,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2076,30 +2068,30 @@
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Shadow Of The Moon (IRE)</t>
+          <t>Stag Night (IRE)</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J29" t="n">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="K29" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="L29" t="n">
-        <v>5.06</v>
+        <v>6.06</v>
       </c>
       <c r="M29" t="n">
         <v>57.94</v>
       </c>
       <c r="N29" t="n">
-        <v>54.8</v>
+        <v>63.7</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2107,7 +2099,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>-2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="30">
@@ -2134,30 +2126,30 @@
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Stag Night (IRE)</t>
+          <t>Eclairage (IRE)</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="K30" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L30" t="n">
-        <v>6.06</v>
+        <v>8.56</v>
       </c>
       <c r="M30" t="n">
         <v>57.94</v>
       </c>
       <c r="N30" t="n">
-        <v>63.7</v>
+        <v>52.3</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2165,7 +2157,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2192,30 +2184,30 @@
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Eclairage (IRE)</t>
+          <t>Buddy Batt (IRE)</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J31" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="K31" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="L31" t="n">
-        <v>8.56</v>
+        <v>16.06</v>
       </c>
       <c r="M31" t="n">
         <v>57.94</v>
       </c>
       <c r="N31" t="n">
-        <v>56.6</v>
+        <v>10.1</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2223,7 +2215,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2249,40 +2241,24 @@
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="n">
-        <v>16</v>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Buddy Batt (IRE)</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>5</v>
-      </c>
-      <c r="J32" t="n">
-        <v>120</v>
-      </c>
-      <c r="K32" t="n">
-        <v>77</v>
-      </c>
-      <c r="L32" t="n">
-        <v>16.06</v>
-      </c>
-      <c r="M32" t="n">
-        <v>57.94</v>
-      </c>
-      <c r="N32" t="n">
-        <v>10.1</v>
-      </c>
+          <t>Gazelle Dor (IRE)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2308,34 +2284,36 @@
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Silk Braid (IRE)</t>
+          <t>Big Gossey (IRE)</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J33" t="n">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
         <v>71.28</v>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>78.2</v>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2362,28 +2340,30 @@
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Big Gossey (IRE)</t>
+          <t>Tango Flare (IRE)</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J34" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="K34" t="n">
-        <v>107</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.75</v>
+      </c>
       <c r="M34" t="n">
         <v>71.28</v>
       </c>
       <c r="N34" t="n">
-        <v>78.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2391,7 +2371,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="35">
@@ -2418,30 +2398,30 @@
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tango Flare (IRE)</t>
+          <t>Bodhi Bear (IRE)</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
         <v>133</v>
       </c>
       <c r="K35" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L35" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="M35" t="n">
         <v>71.28</v>
       </c>
       <c r="N35" t="n">
-        <v>73.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2449,7 +2429,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2476,30 +2456,30 @@
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Bodhi Bear (IRE)</t>
+          <t>Fregada (IRE)</t>
         </is>
       </c>
       <c r="I36" t="n">
         <v>4</v>
       </c>
       <c r="J36" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K36" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="L36" t="n">
-        <v>0.78</v>
+        <v>1.53</v>
       </c>
       <c r="M36" t="n">
         <v>71.28</v>
       </c>
       <c r="N36" t="n">
-        <v>75.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2507,7 +2487,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2534,30 +2514,30 @@
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fregada (IRE)</t>
+          <t>Tahcawin (IRE)</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="K37" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L37" t="n">
-        <v>1.53</v>
+        <v>4.03</v>
       </c>
       <c r="M37" t="n">
         <v>71.28</v>
       </c>
       <c r="N37" t="n">
-        <v>68.40000000000001</v>
+        <v>58.9</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2565,7 +2545,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="38">
@@ -2592,30 +2572,30 @@
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tahcawin (IRE)</t>
+          <t>Temperance (IRE)</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="K38" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L38" t="n">
-        <v>4.03</v>
+        <v>4.53</v>
       </c>
       <c r="M38" t="n">
         <v>71.28</v>
       </c>
       <c r="N38" t="n">
-        <v>58.9</v>
+        <v>61.2</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2623,7 +2603,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2650,30 +2630,30 @@
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Temperance (IRE)</t>
+          <t>Little Queenie (IRE)</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J39" t="n">
         <v>128</v>
       </c>
       <c r="K39" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="L39" t="n">
-        <v>4.53</v>
+        <v>4.68</v>
       </c>
       <c r="M39" t="n">
         <v>71.28</v>
       </c>
       <c r="N39" t="n">
-        <v>61.2</v>
+        <v>60.4</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2708,30 +2688,30 @@
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Little Queenie (IRE)</t>
+          <t>California Dreamer</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
         <v>128</v>
       </c>
       <c r="K40" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="L40" t="n">
-        <v>4.680000000000001</v>
+        <v>5.43</v>
       </c>
       <c r="M40" t="n">
         <v>71.28</v>
       </c>
       <c r="N40" t="n">
-        <v>60.4</v>
+        <v>56.8</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2739,7 +2719,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2766,30 +2746,30 @@
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>California Dreamer</t>
+          <t>Oh Cecelia (IRE)</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="K41" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L41" t="n">
-        <v>5.430000000000001</v>
+        <v>5.58</v>
       </c>
       <c r="M41" t="n">
         <v>71.28</v>
       </c>
       <c r="N41" t="n">
-        <v>56.8</v>
+        <v>53.9</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -2823,40 +2803,24 @@
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="n">
-        <v>9</v>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Oh Cecelia (IRE)</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>3</v>
-      </c>
-      <c r="J42" t="n">
-        <v>121</v>
-      </c>
-      <c r="K42" t="n">
-        <v>101</v>
-      </c>
-      <c r="L42" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="M42" t="n">
-        <v>71.28</v>
-      </c>
-      <c r="N42" t="n">
-        <v>53.9</v>
-      </c>
+          <t>Silk Braid (IRE)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3027,7 +2991,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="46">
@@ -3143,7 +3107,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3239,7 +3203,7 @@
         <v>6</v>
       </c>
       <c r="J49" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="K49" t="n">
         <v>98</v>
@@ -3251,7 +3215,7 @@
         <v>95.48999999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>85.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3259,7 +3223,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3413,7 +3377,7 @@
         <v>4</v>
       </c>
       <c r="J52" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K52" t="n">
         <v>92</v>
@@ -3634,11 +3598,11 @@
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tiberius Thunder (IRE)</t>
+          <t>Purview</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -3648,20 +3612,22 @@
         <v>135</v>
       </c>
       <c r="K56" t="n">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
         <v>123.28</v>
       </c>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="n">
+        <v>98.90000000000001</v>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3688,28 +3654,30 @@
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Purview</t>
+          <t>Trustyourinstinct (IRE)</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J57" t="n">
         <v>135</v>
       </c>
       <c r="K57" t="n">
-        <v>118</v>
-      </c>
-      <c r="L57" t="inlineStr"/>
+        <v>109</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.75</v>
+      </c>
       <c r="M57" t="n">
         <v>123.28</v>
       </c>
       <c r="N57" t="n">
-        <v>98.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3744,30 +3712,30 @@
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Trustyourinstinct (IRE)</t>
+          <t>Hotazhell</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
         <v>135</v>
       </c>
       <c r="K58" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="L58" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="M58" t="n">
         <v>123.28</v>
       </c>
       <c r="N58" t="n">
-        <v>96.40000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3802,30 +3770,30 @@
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
+        <v>4</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Geryon (IRE)</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
         <v>3</v>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Hotazhell</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>4</v>
-      </c>
       <c r="J59" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="K59" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="L59" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M59" t="n">
         <v>123.28</v>
       </c>
       <c r="N59" t="n">
-        <v>93.7</v>
+        <v>89.8</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3833,7 +3801,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="60">
@@ -3860,30 +3828,30 @@
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
+        <v>5</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sindria (IRE)</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
         <v>4</v>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Geryon (IRE)</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
+        <v>132</v>
+      </c>
+      <c r="K60" t="n">
+        <v>100</v>
+      </c>
+      <c r="L60" t="n">
         <v>3</v>
-      </c>
-      <c r="J60" t="n">
-        <v>123</v>
-      </c>
-      <c r="K60" t="n">
-        <v>102</v>
-      </c>
-      <c r="L60" t="n">
-        <v>2</v>
       </c>
       <c r="M60" t="n">
         <v>123.28</v>
       </c>
       <c r="N60" t="n">
-        <v>89.8</v>
+        <v>91.3</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -3891,7 +3859,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3918,30 +3886,30 @@
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sindria (IRE)</t>
+          <t>Isaac Newton (IRE)</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="K61" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L61" t="n">
-        <v>3</v>
+        <v>12.5</v>
       </c>
       <c r="M61" t="n">
         <v>123.28</v>
       </c>
       <c r="N61" t="n">
-        <v>91.3</v>
+        <v>62.9</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -3949,7 +3917,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="62">
@@ -3976,30 +3944,30 @@
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Isaac Newton (IRE)</t>
+          <t>Crown Of Oaks</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J62" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="K62" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L62" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="M62" t="n">
         <v>123.28</v>
       </c>
       <c r="N62" t="n">
-        <v>62.9</v>
+        <v>66</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4007,7 +3975,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4033,40 +4001,24 @@
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="n">
-        <v>7</v>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Crown Of Oaks</t>
-        </is>
-      </c>
-      <c r="I63" t="n">
-        <v>4</v>
-      </c>
-      <c r="J63" t="n">
-        <v>135</v>
-      </c>
-      <c r="K63" t="n">
-        <v>104</v>
-      </c>
-      <c r="L63" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="M63" t="n">
-        <v>123.28</v>
-      </c>
-      <c r="N63" t="n">
-        <v>66</v>
-      </c>
+          <t>Tiberius Thunder (IRE)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P63" t="n">
-        <v>1</v>
-      </c>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4092,34 +4044,36 @@
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Accredited (FR)</t>
+          <t>Zodiac Bear (IRE)</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J64" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="K64" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
         <v>98.88</v>
       </c>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="n">
+        <v>65.90000000000001</v>
+      </c>
       <c r="O64" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="65">
@@ -4146,28 +4100,30 @@
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Zodiac Bear (IRE)</t>
+          <t>Alcantor (FR)</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>135</v>
       </c>
       <c r="K65" t="n">
-        <v>103</v>
-      </c>
-      <c r="L65" t="inlineStr"/>
+        <v>110</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M65" t="n">
         <v>98.88</v>
       </c>
       <c r="N65" t="n">
-        <v>65.90000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4175,7 +4131,7 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4202,30 +4158,30 @@
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Alcantor (FR)</t>
+          <t>Cowardofthecounty (IRE)</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
         <v>135</v>
       </c>
       <c r="K66" t="n">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="L66" t="n">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="M66" t="n">
         <v>98.88</v>
       </c>
       <c r="N66" t="n">
-        <v>68.5</v>
+        <v>63.4</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4233,7 +4189,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4260,30 +4216,30 @@
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Cowardofthecounty (IRE)</t>
+          <t>Spicy Margarita (IRE)</t>
         </is>
       </c>
       <c r="I67" t="n">
         <v>4</v>
       </c>
       <c r="J67" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K67" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="L67" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="M67" t="n">
         <v>98.88</v>
       </c>
       <c r="N67" t="n">
-        <v>63.4</v>
+        <v>62</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4291,7 +4247,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="68">
@@ -4318,24 +4274,24 @@
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Spicy Margarita (IRE)</t>
+          <t>Duckadilly (IRE)</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J68" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K68" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="L68" t="n">
-        <v>1.78</v>
+        <v>2.53</v>
       </c>
       <c r="M68" t="n">
         <v>98.88</v>
@@ -4349,7 +4305,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="69">
@@ -4376,30 +4332,30 @@
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Duckadilly (IRE)</t>
+          <t>Tokenomics (FR)</t>
         </is>
       </c>
       <c r="I69" t="n">
         <v>5</v>
       </c>
       <c r="J69" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K69" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="L69" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="M69" t="n">
         <v>98.88</v>
       </c>
       <c r="N69" t="n">
-        <v>62</v>
+        <v>61.8</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4407,7 +4363,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4433,40 +4389,24 @@
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" t="n">
-        <v>6</v>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tokenomics (FR)</t>
-        </is>
-      </c>
-      <c r="I70" t="n">
-        <v>5</v>
-      </c>
-      <c r="J70" t="n">
-        <v>135</v>
-      </c>
-      <c r="K70" t="n">
-        <v>104</v>
-      </c>
-      <c r="L70" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="M70" t="n">
-        <v>98.88</v>
-      </c>
-      <c r="N70" t="n">
-        <v>61.8</v>
-      </c>
+          <t>Accredited (FR)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4954,34 +4894,36 @@
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bobby Mcgee</t>
+          <t>King Of Earth</t>
         </is>
       </c>
       <c r="I79" t="n">
         <v>3</v>
       </c>
       <c r="J79" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="K79" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="n">
         <v>111.65</v>
       </c>
-      <c r="N79" t="inlineStr"/>
+      <c r="N79" t="n">
+        <v>75.59999999999999</v>
+      </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>-17.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="80">
@@ -5008,34 +4950,38 @@
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Cherry Hill Girl (IRE)</t>
+          <t>Summer Is Tomorrow (IRE)</t>
         </is>
       </c>
       <c r="I80" t="n">
         <v>3</v>
       </c>
       <c r="J80" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="K80" t="n">
-        <v>81</v>
-      </c>
-      <c r="L80" t="inlineStr"/>
+        <v>93</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.15</v>
+      </c>
       <c r="M80" t="n">
         <v>111.65</v>
       </c>
-      <c r="N80" t="inlineStr"/>
+      <c r="N80" t="n">
+        <v>78.40000000000001</v>
+      </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>-17.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5062,28 +5008,30 @@
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>King Of Earth</t>
+          <t>Liberation Date</t>
         </is>
       </c>
       <c r="I81" t="n">
         <v>3</v>
       </c>
       <c r="J81" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="K81" t="n">
-        <v>85</v>
-      </c>
-      <c r="L81" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="L81" t="n">
+        <v>2.15</v>
+      </c>
       <c r="M81" t="n">
         <v>111.65</v>
       </c>
       <c r="N81" t="n">
-        <v>75.59999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -5091,7 +5039,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="82">
@@ -5118,30 +5066,30 @@
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Summer Is Tomorrow (IRE)</t>
+          <t>Howsthebai (IRE)</t>
         </is>
       </c>
       <c r="I82" t="n">
         <v>3</v>
       </c>
       <c r="J82" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K82" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="L82" t="n">
-        <v>0.15</v>
+        <v>2.3</v>
       </c>
       <c r="M82" t="n">
         <v>111.65</v>
       </c>
       <c r="N82" t="n">
-        <v>78.40000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -5176,30 +5124,30 @@
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Liberation Date</t>
+          <t>Rolltight (IRE)</t>
         </is>
       </c>
       <c r="I83" t="n">
         <v>3</v>
       </c>
       <c r="J83" t="n">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="K83" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="L83" t="n">
-        <v>2.15</v>
+        <v>4.3</v>
       </c>
       <c r="M83" t="n">
         <v>111.65</v>
       </c>
       <c r="N83" t="n">
-        <v>63.1</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -5207,7 +5155,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -5234,30 +5182,30 @@
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Howsthebai (IRE)</t>
+          <t>Satoyama (GER)</t>
         </is>
       </c>
       <c r="I84" t="n">
         <v>3</v>
       </c>
       <c r="J84" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K84" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="L84" t="n">
-        <v>2.3</v>
+        <v>4.35</v>
       </c>
       <c r="M84" t="n">
         <v>111.65</v>
       </c>
       <c r="N84" t="n">
-        <v>73.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -5265,7 +5213,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -5292,30 +5240,30 @@
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Rolltight (IRE)</t>
+          <t>Sanctijude (IRE)</t>
         </is>
       </c>
       <c r="I85" t="n">
         <v>3</v>
       </c>
       <c r="J85" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="K85" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L85" t="n">
-        <v>4.3</v>
+        <v>4.85</v>
       </c>
       <c r="M85" t="n">
         <v>111.65</v>
       </c>
       <c r="N85" t="n">
-        <v>66.40000000000001</v>
+        <v>59.6</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -5350,30 +5298,30 @@
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Satoyama (GER)</t>
+          <t>Manton Bay (IRE)</t>
         </is>
       </c>
       <c r="I86" t="n">
         <v>3</v>
       </c>
       <c r="J86" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="K86" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="L86" t="n">
-        <v>4.35</v>
+        <v>5.6</v>
       </c>
       <c r="M86" t="n">
         <v>111.65</v>
       </c>
       <c r="N86" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -5408,30 +5356,30 @@
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Sanctijude (IRE)</t>
+          <t>Monvoe (IRE)</t>
         </is>
       </c>
       <c r="I87" t="n">
         <v>3</v>
       </c>
       <c r="J87" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K87" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L87" t="n">
-        <v>4.85</v>
+        <v>5.65</v>
       </c>
       <c r="M87" t="n">
         <v>111.65</v>
       </c>
       <c r="N87" t="n">
-        <v>59.6</v>
+        <v>58</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -5439,7 +5387,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -5466,30 +5414,30 @@
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Manton Bay (IRE)</t>
+          <t>Stars Will Shine (IRE)</t>
         </is>
       </c>
       <c r="I88" t="n">
         <v>3</v>
       </c>
       <c r="J88" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K88" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L88" t="n">
-        <v>5.6</v>
+        <v>8.149999999999999</v>
       </c>
       <c r="M88" t="n">
         <v>111.65</v>
       </c>
       <c r="N88" t="n">
-        <v>60</v>
+        <v>55.5</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -5497,7 +5445,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -5524,30 +5472,30 @@
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Monvoe (IRE)</t>
+          <t>Brownstown</t>
         </is>
       </c>
       <c r="I89" t="n">
         <v>3</v>
       </c>
       <c r="J89" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="K89" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L89" t="n">
-        <v>5.649999999999999</v>
+        <v>8.649999999999999</v>
       </c>
       <c r="M89" t="n">
         <v>111.65</v>
       </c>
       <c r="N89" t="n">
-        <v>58</v>
+        <v>55.2</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -5555,7 +5503,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="90">
@@ -5582,30 +5530,30 @@
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Stars Will Shine (IRE)</t>
+          <t>Antigua (IRE)</t>
         </is>
       </c>
       <c r="I90" t="n">
         <v>3</v>
       </c>
       <c r="J90" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="K90" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="L90" t="n">
-        <v>8.15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M90" t="n">
         <v>111.65</v>
       </c>
       <c r="N90" t="n">
-        <v>55.5</v>
+        <v>55.2</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -5613,7 +5561,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="91">
@@ -5640,30 +5588,30 @@
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Brownstown</t>
+          <t>Punica Granatum (IRE)</t>
         </is>
       </c>
       <c r="I91" t="n">
         <v>3</v>
       </c>
       <c r="J91" t="n">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="K91" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="L91" t="n">
-        <v>8.65</v>
+        <v>10.55</v>
       </c>
       <c r="M91" t="n">
         <v>111.65</v>
       </c>
       <c r="N91" t="n">
-        <v>55.2</v>
+        <v>40.2</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -5671,7 +5619,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>-0.5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="92">
@@ -5698,30 +5646,30 @@
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Antigua (IRE)</t>
+          <t>Ryefield Dasher (IRE)</t>
         </is>
       </c>
       <c r="I92" t="n">
         <v>3</v>
       </c>
       <c r="J92" t="n">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="K92" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="L92" t="n">
-        <v>8.800000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="M92" t="n">
         <v>111.65</v>
       </c>
       <c r="N92" t="n">
-        <v>55.2</v>
+        <v>37.8</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -5729,7 +5677,7 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0.5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="93">
@@ -5756,30 +5704,30 @@
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Punica Granatum (IRE)</t>
+          <t>Listentodwindblow (IRE)</t>
         </is>
       </c>
       <c r="I93" t="n">
         <v>3</v>
       </c>
       <c r="J93" t="n">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="K93" t="n">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="L93" t="n">
-        <v>10.55</v>
+        <v>10.8</v>
       </c>
       <c r="M93" t="n">
         <v>111.65</v>
       </c>
       <c r="N93" t="n">
-        <v>40.2</v>
+        <v>50.7</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -5787,7 +5735,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -5814,30 +5762,30 @@
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Ryefield Dasher (IRE)</t>
+          <t>Anushka (IRE)</t>
         </is>
       </c>
       <c r="I94" t="n">
         <v>3</v>
       </c>
       <c r="J94" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K94" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L94" t="n">
-        <v>10.7</v>
+        <v>10.95</v>
       </c>
       <c r="M94" t="n">
         <v>111.65</v>
       </c>
       <c r="N94" t="n">
-        <v>39.5</v>
+        <v>41.6</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -5845,7 +5793,7 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -5871,40 +5819,24 @@
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="n">
-        <v>15</v>
-      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Listentodwindblow (IRE)</t>
-        </is>
-      </c>
-      <c r="I95" t="n">
-        <v>3</v>
-      </c>
-      <c r="J95" t="n">
-        <v>138</v>
-      </c>
-      <c r="K95" t="n">
-        <v>103</v>
-      </c>
-      <c r="L95" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="M95" t="n">
-        <v>111.65</v>
-      </c>
-      <c r="N95" t="n">
-        <v>50.7</v>
-      </c>
+          <t>Bobby Mcgee</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="P95" t="n">
-        <v>2</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5929,40 +5861,24 @@
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="n">
-        <v>16</v>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Anushka (IRE)</t>
-        </is>
-      </c>
-      <c r="I96" t="n">
-        <v>3</v>
-      </c>
-      <c r="J96" t="n">
-        <v>122</v>
-      </c>
-      <c r="K96" t="n">
-        <v>80</v>
-      </c>
-      <c r="L96" t="n">
-        <v>10.95</v>
-      </c>
-      <c r="M96" t="n">
-        <v>111.65</v>
-      </c>
-      <c r="N96" t="n">
-        <v>41.6</v>
-      </c>
+          <t>Cherry Hill Girl (IRE)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="P96" t="n">
-        <v>2</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5988,34 +5904,36 @@
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Truth Be Told (IRE)</t>
+          <t>In My Teens (IRE)</t>
         </is>
       </c>
       <c r="I97" t="n">
         <v>4</v>
       </c>
       <c r="J97" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="K97" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="n">
         <v>150.14</v>
       </c>
-      <c r="N97" t="inlineStr"/>
+      <c r="N97" t="n">
+        <v>91.8</v>
+      </c>
       <c r="O97" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -6042,28 +5960,30 @@
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>In My Teens (IRE)</t>
+          <t>This Songisforyou (USA)</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J98" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K98" t="n">
-        <v>96</v>
-      </c>
-      <c r="L98" t="inlineStr"/>
+        <v>97</v>
+      </c>
+      <c r="L98" t="n">
+        <v>7</v>
+      </c>
       <c r="M98" t="n">
         <v>150.14</v>
       </c>
       <c r="N98" t="n">
-        <v>91.8</v>
+        <v>75.8</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -6098,30 +6018,30 @@
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>This Songisforyou (USA)</t>
+          <t>The Real Screamer (IRE)</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J99" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="K99" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="L99" t="n">
-        <v>7</v>
+        <v>8.75</v>
       </c>
       <c r="M99" t="n">
         <v>150.14</v>
       </c>
       <c r="N99" t="n">
-        <v>75.8</v>
+        <v>74</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -6156,30 +6076,30 @@
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>The Real Screamer (IRE)</t>
+          <t>Navy Waters (IRE)</t>
         </is>
       </c>
       <c r="I100" t="n">
         <v>5</v>
       </c>
       <c r="J100" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="K100" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L100" t="n">
-        <v>8.75</v>
+        <v>9.5</v>
       </c>
       <c r="M100" t="n">
         <v>150.14</v>
       </c>
       <c r="N100" t="n">
-        <v>74</v>
+        <v>68.5</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -6187,7 +6107,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="101">
@@ -6214,30 +6134,30 @@
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Navy Waters (IRE)</t>
+          <t>Star Harbour (IRE)</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J101" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K101" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="L101" t="n">
-        <v>9.5</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M101" t="n">
         <v>150.14</v>
       </c>
       <c r="N101" t="n">
-        <v>68.5</v>
+        <v>69.5</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -6245,7 +6165,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -6272,30 +6192,30 @@
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Star Harbour (IRE)</t>
+          <t>Marazion (IRE)</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J102" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K102" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L102" t="n">
-        <v>9.529999999999999</v>
+        <v>10.78</v>
       </c>
       <c r="M102" t="n">
         <v>150.14</v>
       </c>
       <c r="N102" t="n">
-        <v>69.5</v>
+        <v>65.2</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -6303,7 +6223,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="103">
@@ -6330,30 +6250,30 @@
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Marazion (IRE)</t>
+          <t>Retracement (IRE)</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J103" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K103" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L103" t="n">
-        <v>10.78</v>
+        <v>10.93</v>
       </c>
       <c r="M103" t="n">
         <v>150.14</v>
       </c>
       <c r="N103" t="n">
-        <v>65.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -6388,30 +6308,30 @@
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Retracement (IRE)</t>
+          <t>Dawn Rising (IRE)</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J104" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="K104" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="L104" t="n">
-        <v>10.93</v>
+        <v>11.43</v>
       </c>
       <c r="M104" t="n">
         <v>150.14</v>
       </c>
       <c r="N104" t="n">
-        <v>64.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -6419,7 +6339,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -6446,30 +6366,30 @@
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Dawn Rising (IRE)</t>
+          <t>Railwayview Lady (IRE)</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J105" t="n">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="K105" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="L105" t="n">
-        <v>11.43</v>
+        <v>14.68</v>
       </c>
       <c r="M105" t="n">
         <v>150.14</v>
       </c>
       <c r="N105" t="n">
-        <v>68.09999999999999</v>
+        <v>54.2</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -6477,7 +6397,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="106">
@@ -6504,30 +6424,30 @@
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Railwayview Lady (IRE)</t>
+          <t>Cloud Seeker</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J106" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="K106" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="L106" t="n">
-        <v>14.68</v>
+        <v>18.18</v>
       </c>
       <c r="M106" t="n">
         <v>150.14</v>
       </c>
       <c r="N106" t="n">
-        <v>54.2</v>
+        <v>50.8</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -6562,38 +6482,38 @@
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Cloud Seeker</t>
+          <t>Whats Your Game (IRE)</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J107" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K107" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="L107" t="n">
-        <v>18.18</v>
+        <v>29.18</v>
       </c>
       <c r="M107" t="n">
         <v>150.14</v>
       </c>
       <c r="N107" t="n">
-        <v>50.8</v>
+        <v>57.1</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -6620,30 +6540,30 @@
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Whats Your Game (IRE)</t>
+          <t>Obscenity (IRE)</t>
         </is>
       </c>
       <c r="I108" t="n">
         <v>4</v>
       </c>
       <c r="J108" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K108" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L108" t="n">
-        <v>29.18</v>
+        <v>29.28</v>
       </c>
       <c r="M108" t="n">
         <v>150.14</v>
       </c>
       <c r="N108" t="n">
-        <v>57.1</v>
+        <v>56.7</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -6678,30 +6598,30 @@
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Obscenity (IRE)</t>
+          <t>Factual Fact (FR)</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J109" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K109" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L109" t="n">
-        <v>29.28</v>
+        <v>37.28</v>
       </c>
       <c r="M109" t="n">
         <v>150.14</v>
       </c>
       <c r="N109" t="n">
-        <v>56.7</v>
+        <v>50.3</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -6709,7 +6629,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -6735,40 +6655,24 @@
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="n">
-        <v>13</v>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Factual Fact (FR)</t>
-        </is>
-      </c>
-      <c r="I110" t="n">
-        <v>7</v>
-      </c>
-      <c r="J110" t="n">
-        <v>130</v>
-      </c>
-      <c r="K110" t="n">
-        <v>89</v>
-      </c>
-      <c r="L110" t="n">
-        <v>37.28</v>
-      </c>
-      <c r="M110" t="n">
-        <v>150.14</v>
-      </c>
-      <c r="N110" t="n">
-        <v>50.3</v>
-      </c>
+          <t>Truth Be Told (IRE)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P110" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6807,7 +6711,7 @@
         <v>3</v>
       </c>
       <c r="J111" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -6817,7 +6721,7 @@
         <v>122.06</v>
       </c>
       <c r="N111" t="n">
-        <v>51.3</v>
+        <v>46.1</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -6825,7 +6729,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="112">
@@ -7005,7 +6909,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -7703,7 +7607,7 @@
         <v>3</v>
       </c>
       <c r="J126" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K126" t="n">
         <v>64</v>
@@ -7715,7 +7619,7 @@
         <v>121.15</v>
       </c>
       <c r="N126" t="n">
-        <v>54.1</v>
+        <v>51.3</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -8261,7 +8165,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="136">
@@ -8321,7 +8225,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -8361,7 +8265,7 @@
         <v>4</v>
       </c>
       <c r="J137" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -8373,7 +8277,7 @@
         <v>88.63</v>
       </c>
       <c r="N137" t="n">
-        <v>45.9</v>
+        <v>44.9</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -8421,7 +8325,7 @@
         <v>3</v>
       </c>
       <c r="J138" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -8433,7 +8337,7 @@
         <v>88.63</v>
       </c>
       <c r="N138" t="n">
-        <v>35.3</v>
+        <v>32.6</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -8441,7 +8345,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="139">
@@ -8481,7 +8385,7 @@
         <v>3</v>
       </c>
       <c r="J139" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -8493,7 +8397,7 @@
         <v>88.63</v>
       </c>
       <c r="N139" t="n">
-        <v>44.6</v>
+        <v>37.9</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -8501,7 +8405,7 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -8561,7 +8465,7 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
@@ -8601,7 +8505,7 @@
         <v>3</v>
       </c>
       <c r="J141" t="n">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -8613,7 +8517,7 @@
         <v>88.63</v>
       </c>
       <c r="N141" t="n">
-        <v>32.2</v>
+        <v>25.9</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -8681,7 +8585,7 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -8781,7 +8685,7 @@
         <v>6</v>
       </c>
       <c r="J144" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K144" t="n">
         <v>60</v>
@@ -8791,7 +8695,7 @@
         <v>222.15</v>
       </c>
       <c r="N144" t="n">
-        <v>42.5</v>
+        <v>35.2</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -8899,10 +8803,10 @@
         <v>5</v>
       </c>
       <c r="J146" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="K146" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L146" t="n">
         <v>14.75</v>
@@ -8911,7 +8815,7 @@
         <v>222.15</v>
       </c>
       <c r="N146" t="n">
-        <v>9.1</v>
+        <v>1.7</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -8919,7 +8823,7 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="147">
@@ -8959,7 +8863,7 @@
         <v>8</v>
       </c>
       <c r="J147" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="K147" t="n">
         <v>57</v>
@@ -8971,7 +8875,7 @@
         <v>222.15</v>
       </c>
       <c r="N147" t="n">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -8979,7 +8883,7 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -9019,7 +8923,7 @@
         <v>4</v>
       </c>
       <c r="J148" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K148" t="n">
         <v>47</v>
@@ -9031,7 +8935,7 @@
         <v>222.15</v>
       </c>
       <c r="N148" t="n">
-        <v>-1.2</v>
+        <v>-4.5</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -9248,34 +9152,36 @@
         <v>6</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Thanks Dad</t>
+          <t>Trust Sergei</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J152" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K152" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="n">
         <v>74.38</v>
       </c>
-      <c r="N152" t="inlineStr"/>
+      <c r="N152" t="n">
+        <v>65.09999999999999</v>
+      </c>
       <c r="O152" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>-13</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="153">
@@ -9304,28 +9210,30 @@
         <v>6</v>
       </c>
       <c r="G153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Trust Sergei</t>
+          <t>On Key</t>
         </is>
       </c>
       <c r="I153" t="n">
         <v>4</v>
       </c>
       <c r="J153" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K153" t="n">
-        <v>54</v>
-      </c>
-      <c r="L153" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M153" t="n">
         <v>74.38</v>
       </c>
       <c r="N153" t="n">
-        <v>65.09999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -9362,30 +9270,30 @@
         <v>6</v>
       </c>
       <c r="G154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>On Key</t>
+          <t>Master Dandy (IRE)</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J154" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K154" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L154" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="M154" t="n">
         <v>74.38</v>
       </c>
       <c r="N154" t="n">
-        <v>64.7</v>
+        <v>65.5</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -9393,7 +9301,7 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
@@ -9422,30 +9330,30 @@
         <v>6</v>
       </c>
       <c r="G155" t="n">
+        <v>4</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sunlit Sea</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
         <v>3</v>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Master Dandy (IRE)</t>
-        </is>
-      </c>
-      <c r="I155" t="n">
-        <v>6</v>
-      </c>
       <c r="J155" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="K155" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L155" t="n">
-        <v>0.13</v>
+        <v>1.88</v>
       </c>
       <c r="M155" t="n">
         <v>74.38</v>
       </c>
       <c r="N155" t="n">
-        <v>65.5</v>
+        <v>62.9</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -9453,7 +9361,7 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -9482,30 +9390,30 @@
         <v>6</v>
       </c>
       <c r="G156" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Sunlit Sea</t>
+          <t>Porfin (IRE)</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J156" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K156" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="L156" t="n">
-        <v>1.88</v>
+        <v>3.63</v>
       </c>
       <c r="M156" t="n">
         <v>74.38</v>
       </c>
       <c r="N156" t="n">
-        <v>62.9</v>
+        <v>47.2</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -9513,7 +9421,7 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="157">
@@ -9542,30 +9450,30 @@
         <v>6</v>
       </c>
       <c r="G157" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Porfin (IRE)</t>
+          <t>Alafdhal (IRE)</t>
         </is>
       </c>
       <c r="I157" t="n">
         <v>8</v>
       </c>
       <c r="J157" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="K157" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="L157" t="n">
-        <v>3.63</v>
+        <v>4.63</v>
       </c>
       <c r="M157" t="n">
         <v>74.38</v>
       </c>
       <c r="N157" t="n">
-        <v>47.2</v>
+        <v>51.9</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -9573,7 +9481,7 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -9602,30 +9510,30 @@
         <v>6</v>
       </c>
       <c r="G158" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Alafdhal (IRE)</t>
+          <t>Barry The Worm</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J158" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="K158" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L158" t="n">
-        <v>4.63</v>
+        <v>5.38</v>
       </c>
       <c r="M158" t="n">
         <v>74.38</v>
       </c>
       <c r="N158" t="n">
-        <v>51.9</v>
+        <v>52.2</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -9633,7 +9541,7 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -9662,30 +9570,30 @@
         <v>6</v>
       </c>
       <c r="G159" t="n">
+        <v>8</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>White Umbrella</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
         <v>7</v>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Barry The Worm</t>
-        </is>
-      </c>
-      <c r="I159" t="n">
-        <v>3</v>
-      </c>
       <c r="J159" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K159" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L159" t="n">
-        <v>5.38</v>
+        <v>5.53</v>
       </c>
       <c r="M159" t="n">
         <v>74.38</v>
       </c>
       <c r="N159" t="n">
-        <v>52.2</v>
+        <v>48.7</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
@@ -9693,7 +9601,7 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -9722,30 +9630,30 @@
         <v>6</v>
       </c>
       <c r="G160" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>White Umbrella</t>
+          <t>King David (IRE)</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J160" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K160" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L160" t="n">
-        <v>5.53</v>
+        <v>7.029999999999999</v>
       </c>
       <c r="M160" t="n">
         <v>74.38</v>
       </c>
       <c r="N160" t="n">
-        <v>48.7</v>
+        <v>46.6</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
@@ -9753,7 +9661,7 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -9782,30 +9690,30 @@
         <v>6</v>
       </c>
       <c r="G161" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>King David (IRE)</t>
+          <t>Teardrops</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J161" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="K161" t="n">
         <v>58</v>
       </c>
       <c r="L161" t="n">
-        <v>7.029999999999999</v>
+        <v>7.18</v>
       </c>
       <c r="M161" t="n">
         <v>74.38</v>
       </c>
       <c r="N161" t="n">
-        <v>46.6</v>
+        <v>40.7</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
@@ -9842,30 +9750,30 @@
         <v>6</v>
       </c>
       <c r="G162" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Teardrops</t>
+          <t>Em Jay Kay</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J162" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K162" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L162" t="n">
-        <v>7.18</v>
+        <v>11.43</v>
       </c>
       <c r="M162" t="n">
         <v>74.38</v>
       </c>
       <c r="N162" t="n">
-        <v>46.3</v>
+        <v>34</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
@@ -9902,30 +9810,30 @@
         <v>6</v>
       </c>
       <c r="G163" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Em Jay Kay</t>
+          <t>Last Outlaw (IRE)</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J163" t="n">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="K163" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L163" t="n">
-        <v>11.43</v>
+        <v>18.43</v>
       </c>
       <c r="M163" t="n">
         <v>74.38</v>
       </c>
       <c r="N163" t="n">
-        <v>34</v>
+        <v>7.1</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
@@ -9961,40 +9869,24 @@
       <c r="F164" t="n">
         <v>6</v>
       </c>
-      <c r="G164" t="n">
-        <v>12</v>
-      </c>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Last Outlaw (IRE)</t>
-        </is>
-      </c>
-      <c r="I164" t="n">
-        <v>5</v>
-      </c>
-      <c r="J164" t="n">
-        <v>132</v>
-      </c>
-      <c r="K164" t="n">
-        <v>52</v>
-      </c>
-      <c r="L164" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="M164" t="n">
-        <v>74.38</v>
-      </c>
-      <c r="N164" t="n">
-        <v>7.1</v>
-      </c>
+          <t>Thanks Dad</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P164" t="n">
-        <v>0</v>
-      </c>
+      <c r="P164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10211,7 +10103,7 @@
         <v>8</v>
       </c>
       <c r="J168" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K168" t="n">
         <v>65</v>
@@ -10223,7 +10115,7 @@
         <v>61.5</v>
       </c>
       <c r="N168" t="n">
-        <v>53.3</v>
+        <v>53.1</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
@@ -10320,34 +10212,36 @@
         <v>6</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Mythical Isle (IRE)</t>
+          <t>Lessay (IRE)</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J170" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K170" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="n">
         <v>89.54000000000001</v>
       </c>
-      <c r="N170" t="inlineStr"/>
+      <c r="N170" t="n">
+        <v>47.1</v>
+      </c>
       <c r="O170" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P170" t="n">
-        <v>-10</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="171">
@@ -10376,28 +10270,30 @@
         <v>6</v>
       </c>
       <c r="G171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Lessay (IRE)</t>
+          <t>Cooramook (IRE)</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J171" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K171" t="n">
-        <v>56</v>
-      </c>
-      <c r="L171" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="L171" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M171" t="n">
         <v>89.54000000000001</v>
       </c>
       <c r="N171" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
@@ -10434,30 +10330,30 @@
         <v>6</v>
       </c>
       <c r="G172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Cooramook (IRE)</t>
+          <t>Pearly Squirrel (IRE)</t>
         </is>
       </c>
       <c r="I172" t="n">
         <v>4</v>
       </c>
       <c r="J172" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K172" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L172" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="M172" t="n">
         <v>89.54000000000001</v>
       </c>
       <c r="N172" t="n">
-        <v>51.5</v>
+        <v>51.7</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
@@ -10465,7 +10361,7 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -10494,30 +10390,30 @@
         <v>6</v>
       </c>
       <c r="G173" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Pearly Squirrel (IRE)</t>
+          <t>Split Elevens</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J173" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K173" t="n">
         <v>62</v>
       </c>
       <c r="L173" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="M173" t="n">
         <v>89.54000000000001</v>
       </c>
       <c r="N173" t="n">
-        <v>51.7</v>
+        <v>48.3</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -10554,30 +10450,30 @@
         <v>6</v>
       </c>
       <c r="G174" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Split Elevens</t>
+          <t>Harbour Vision</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J174" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K174" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="L174" t="n">
-        <v>2.9</v>
+        <v>4.65</v>
       </c>
       <c r="M174" t="n">
         <v>89.54000000000001</v>
       </c>
       <c r="N174" t="n">
-        <v>50.3</v>
+        <v>44.5</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
@@ -10585,7 +10481,7 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="175">
@@ -10614,30 +10510,30 @@
         <v>6</v>
       </c>
       <c r="G175" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Harbour Vision</t>
+          <t>Bomb Squad (IRE)</t>
         </is>
       </c>
       <c r="I175" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J175" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K175" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="L175" t="n">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="M175" t="n">
         <v>89.54000000000001</v>
       </c>
       <c r="N175" t="n">
-        <v>44.5</v>
+        <v>46.2</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
@@ -10645,7 +10541,7 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -10674,30 +10570,30 @@
         <v>6</v>
       </c>
       <c r="G176" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Bomb Squad (IRE)</t>
+          <t>Skellig Isle</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J176" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K176" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L176" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="M176" t="n">
         <v>89.54000000000001</v>
       </c>
       <c r="N176" t="n">
-        <v>46.2</v>
+        <v>42.4</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -10705,7 +10601,7 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -10734,30 +10630,30 @@
         <v>6</v>
       </c>
       <c r="G177" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Skellig Isle</t>
+          <t>Faster Bee</t>
         </is>
       </c>
       <c r="I177" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J177" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K177" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="L177" t="n">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="M177" t="n">
         <v>89.54000000000001</v>
       </c>
       <c r="N177" t="n">
-        <v>42.4</v>
+        <v>37.3</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
@@ -10794,15 +10690,15 @@
         <v>6</v>
       </c>
       <c r="G178" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Faster Bee</t>
+          <t>Clover Time</t>
         </is>
       </c>
       <c r="I178" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J178" t="n">
         <v>129</v>
@@ -10811,13 +10707,13 @@
         <v>57</v>
       </c>
       <c r="L178" t="n">
-        <v>6.25</v>
+        <v>14.75</v>
       </c>
       <c r="M178" t="n">
         <v>89.54000000000001</v>
       </c>
       <c r="N178" t="n">
-        <v>37.3</v>
+        <v>15.7</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
@@ -10853,40 +10749,24 @@
       <c r="F179" t="n">
         <v>6</v>
       </c>
-      <c r="G179" t="n">
-        <v>9</v>
-      </c>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Clover Time</t>
-        </is>
-      </c>
-      <c r="I179" t="n">
-        <v>4</v>
-      </c>
-      <c r="J179" t="n">
-        <v>129</v>
-      </c>
-      <c r="K179" t="n">
-        <v>57</v>
-      </c>
-      <c r="L179" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="M179" t="n">
-        <v>89.54000000000001</v>
-      </c>
-      <c r="N179" t="n">
-        <v>15.7</v>
-      </c>
+          <t>Mythical Isle (IRE)</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P179" t="n">
-        <v>0</v>
-      </c>
+      <c r="P179" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
